--- a/tests/reports/load_test_report.xlsx
+++ b/tests/reports/load_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4312,12 @@
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>7ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>3ms</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7282,12 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>0ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7552,12 @@
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7822,12 +7822,12 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8200,12 +8200,12 @@
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8416,12 +8416,12 @@
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>3ms</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11768,12 +11768,12 @@
       </c>
       <c r="I204" s="14" t="inlineStr">
         <is>
-          <t>6ms</t>
+          <t>5ms</t>
         </is>
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12092,12 +12092,12 @@
       </c>
       <c r="I210" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12200,12 +12200,12 @@
       </c>
       <c r="I212" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12362,12 +12362,12 @@
       </c>
       <c r="I215" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12416,12 +12416,12 @@
       </c>
       <c r="I216" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12470,12 +12470,12 @@
       </c>
       <c r="I217" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12524,12 +12524,12 @@
       </c>
       <c r="I218" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12578,12 +12578,12 @@
       </c>
       <c r="I219" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I220" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12686,12 +12686,12 @@
       </c>
       <c r="I221" s="16" t="inlineStr">
         <is>
-          <t>5ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="I222" s="14" t="inlineStr">
         <is>
-          <t>8ms</t>
+          <t>6ms</t>
         </is>
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="I223" s="16" t="inlineStr">
         <is>
-          <t>7ms</t>
+          <t>8ms</t>
         </is>
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12848,12 +12848,12 @@
       </c>
       <c r="I224" s="14" t="inlineStr">
         <is>
-          <t>12ms</t>
+          <t>9ms</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12902,12 +12902,12 @@
       </c>
       <c r="I225" s="16" t="inlineStr">
         <is>
-          <t>16ms</t>
+          <t>14ms</t>
         </is>
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -12956,12 +12956,12 @@
       </c>
       <c r="I226" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13118,12 +13118,12 @@
       </c>
       <c r="I229" s="16" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13172,12 +13172,12 @@
       </c>
       <c r="I230" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14360,12 +14360,12 @@
       </c>
       <c r="I252" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15013,7 +15013,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15283,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="I288" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="I289" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16844,12 +16844,12 @@
       </c>
       <c r="I298" s="14" t="inlineStr">
         <is>
-          <t>5ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16898,12 +16898,12 @@
       </c>
       <c r="I299" s="16" t="inlineStr">
         <is>
-          <t>8ms</t>
+          <t>7ms</t>
         </is>
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -16952,12 +16952,12 @@
       </c>
       <c r="I300" s="14" t="inlineStr">
         <is>
-          <t>11ms</t>
+          <t>10ms</t>
         </is>
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:42</t>
+          <t>2026-07-23 20:08:54</t>
         </is>
       </c>
     </row>

--- a/tests/reports/load_test_report.xlsx
+++ b/tests/reports/load_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5122,12 +5122,12 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6256,12 +6256,12 @@
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6904,12 +6904,12 @@
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7282,12 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7606,12 +7606,12 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8038,12 +8038,12 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8092,12 +8092,12 @@
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8308,12 +8308,12 @@
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8416,12 +8416,12 @@
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8524,12 @@
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8578,12 +8578,12 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8632,12 @@
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11606,12 +11606,12 @@
       </c>
       <c r="I201" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11660,12 +11660,12 @@
       </c>
       <c r="I202" s="14" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="I203" s="16" t="inlineStr">
         <is>
-          <t>5ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11768,12 +11768,12 @@
       </c>
       <c r="I204" s="14" t="inlineStr">
         <is>
-          <t>5ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       </c>
       <c r="I206" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11930,12 +11930,12 @@
       </c>
       <c r="I207" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12038,12 +12038,12 @@
       </c>
       <c r="I209" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12146,12 +12146,12 @@
       </c>
       <c r="I211" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="I213" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12362,12 +12362,12 @@
       </c>
       <c r="I215" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12470,12 +12470,12 @@
       </c>
       <c r="I217" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12578,12 +12578,12 @@
       </c>
       <c r="I219" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I220" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12686,12 +12686,12 @@
       </c>
       <c r="I221" s="16" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="I222" s="14" t="inlineStr">
         <is>
-          <t>6ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="I223" s="16" t="inlineStr">
         <is>
-          <t>8ms</t>
+          <t>3ms</t>
         </is>
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12848,12 +12848,12 @@
       </c>
       <c r="I224" s="14" t="inlineStr">
         <is>
-          <t>9ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12902,12 +12902,12 @@
       </c>
       <c r="I225" s="16" t="inlineStr">
         <is>
-          <t>14ms</t>
+          <t>7ms</t>
         </is>
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -12956,12 +12956,12 @@
       </c>
       <c r="I226" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13010,12 +13010,12 @@
       </c>
       <c r="I227" s="16" t="inlineStr">
         <is>
-          <t>6ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13118,12 +13118,12 @@
       </c>
       <c r="I229" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14360,12 +14360,12 @@
       </c>
       <c r="I252" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15013,7 +15013,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15283,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16250,12 +16250,12 @@
       </c>
       <c r="I287" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="I288" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="I289" s="16" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16466,12 +16466,12 @@
       </c>
       <c r="I291" s="16" t="inlineStr">
         <is>
-          <t>1ms</t>
+          <t>0ms</t>
         </is>
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16628,12 +16628,12 @@
       </c>
       <c r="I294" s="14" t="inlineStr">
         <is>
-          <t>2ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16790,12 +16790,12 @@
       </c>
       <c r="I297" s="16" t="inlineStr">
         <is>
-          <t>3ms</t>
+          <t>1ms</t>
         </is>
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16844,12 +16844,12 @@
       </c>
       <c r="I298" s="14" t="inlineStr">
         <is>
-          <t>4ms</t>
+          <t>2ms</t>
         </is>
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16898,12 +16898,12 @@
       </c>
       <c r="I299" s="16" t="inlineStr">
         <is>
-          <t>7ms</t>
+          <t>3ms</t>
         </is>
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -16952,12 +16952,12 @@
       </c>
       <c r="I300" s="14" t="inlineStr">
         <is>
-          <t>10ms</t>
+          <t>4ms</t>
         </is>
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:54</t>
+          <t>2026-07-24 08:35:01</t>
         </is>
       </c>
     </row>
